--- a/ig/DM_FINESS_New/ValueSet-jdv-j377-categorie-entite-geographique-exercice-ror.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j377-categorie-entite-geographique-exercice-ror.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T18:02:28.249+00:00</t>
+    <t>2026-02-23T18:02:28.249+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Catégories d'établissements FINESS ou hors FINESS et secteurs d'activité des cabinets</t>
+    <t>Ce JDV remplace le JDV_J55_CategorieEG_ROR</t>
   </si>
   <si>
     <t>Purpose</t>
